--- a/artfynd/A 6469-2022 artfynd.xlsx
+++ b/artfynd/A 6469-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6469-2022 artfynd.xlsx
+++ b/artfynd/A 6469-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96479058</v>
+        <v>104112687</v>
       </c>
       <c r="B2" t="n">
-        <v>90139</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1975</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långa komyr, Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318251.5201410252</v>
+        <v>318470</v>
       </c>
       <c r="R2" t="n">
-        <v>6554964.793886489</v>
+        <v>6555140</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +783,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -815,57 +801,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96480542</v>
+        <v>96534476</v>
       </c>
       <c r="B3" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>1036</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SV om Stora Stickshöjden, Dls</t>
+          <t>Långa komyr, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318475.658278471</v>
+        <v>318233</v>
       </c>
       <c r="R3" t="n">
-        <v>6555212.435965576</v>
+        <v>6554996</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,22 +873,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,22 +893,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Mosse</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Levande trä # Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -955,37 +926,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96480625</v>
+        <v>96481015</v>
       </c>
       <c r="B4" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1002,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>318460.0960347397</v>
+        <v>318538</v>
       </c>
       <c r="R4" t="n">
-        <v>6555145.258387837</v>
+        <v>6555205</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1035,19 +1001,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1095,15 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96481015</v>
+        <v>104112477</v>
       </c>
       <c r="B5" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,14 +1089,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SV om Stora Stickshöjden, Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>318537.6901169894</v>
+        <v>318419</v>
       </c>
       <c r="R5" t="n">
-        <v>6555205.373153843</v>
+        <v>6555118</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1172,22 +1123,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1217,7 +1158,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1235,53 +1176,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98968896</v>
+        <v>96437745</v>
       </c>
       <c r="B6" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>1975</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>Moltemyren, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>318605.2548142547</v>
+        <v>318177</v>
       </c>
       <c r="R6" t="n">
-        <v>6555314.842466146</v>
+        <v>6554880</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1305,22 +1248,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,71 +1262,94 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog, mosskant</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98968883</v>
+        <v>96473689</v>
       </c>
       <c r="B7" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>1975</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>318643.7216017609</v>
+        <v>318589</v>
       </c>
       <c r="R7" t="n">
-        <v>6555332.567340311</v>
+        <v>6555252</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1417,22 +1373,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1441,71 +1387,94 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98968882</v>
+        <v>96477946</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1975</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>318637.2093800205</v>
+        <v>318546</v>
       </c>
       <c r="R8" t="n">
-        <v>6555325.673474086</v>
+        <v>6555211</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1529,22 +1498,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1553,86 +1512,94 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98968886</v>
+        <v>96478254</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1975</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>318703.9193163954</v>
+        <v>318432</v>
       </c>
       <c r="R9" t="n">
-        <v>6555406.369873124</v>
+        <v>6555102</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1656,22 +1623,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,86 +1637,94 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98968865</v>
+        <v>96478596</v>
       </c>
       <c r="B10" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>1975</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>SV om Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>318447.440212062</v>
+        <v>318301</v>
       </c>
       <c r="R10" t="n">
-        <v>6555117.560631151</v>
+        <v>6554944</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1783,22 +1748,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1807,55 +1762,71 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101934224</v>
+        <v>96479058</v>
       </c>
       <c r="B11" t="n">
-        <v>89851</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5467</v>
+        <v>1975</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1868,14 +1839,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder om Långa Komyr, Dls</t>
+          <t>Långa komyr, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>318287.3002075547</v>
+        <v>318252</v>
       </c>
       <c r="R11" t="n">
-        <v>6554969.266814172</v>
+        <v>6554965</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1902,22 +1873,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1958,63 +1919,62 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bård E. Andersen, Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101933733</v>
+        <v>96479440</v>
       </c>
       <c r="B12" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5685</v>
+        <v>1975</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långa Komyr, Dls</t>
+          <t>SV om Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>318246.1543473901</v>
+        <v>318236</v>
       </c>
       <c r="R12" t="n">
-        <v>6554982.02937214</v>
+        <v>6554927</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2038,22 +1998,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2068,7 +2018,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Blåbärbarrskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2089,68 +2039,67 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tommy Solberg, Bård E. Andersen</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101934034</v>
+        <v>96479552</v>
       </c>
       <c r="B13" t="n">
-        <v>89851</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5467</v>
+        <v>1975</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långa Komyr., Dls</t>
+          <t>SV om Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>318350.5700090727</v>
+        <v>318235</v>
       </c>
       <c r="R13" t="n">
-        <v>6555053.216907648</v>
+        <v>6554917</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2174,22 +2123,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2204,80 +2143,81 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Blåbärbarrskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Låga</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tommy Solberg, Bård E. Andersen</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101934233</v>
+        <v>104073740</v>
       </c>
       <c r="B14" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>1975</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söder om Långa Komyr, Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>318287.3002075547</v>
+        <v>318526</v>
       </c>
       <c r="R14" t="n">
-        <v>6554969.266814172</v>
+        <v>6555188</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2304,22 +2244,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2334,7 +2264,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Bärbarrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2355,69 +2285,67 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bård E. Andersen, Tommy Solberg</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101933803</v>
+        <v>104104854</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1975</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långa Komyr S., Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>318265.4567616634</v>
+        <v>318361</v>
       </c>
       <c r="R15" t="n">
-        <v>6554954.354472333</v>
+        <v>6555092</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2441,22 +2369,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2471,74 +2389,88 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Bär- och ljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tommy Solberg, Bård E. Andersen</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101934586</v>
+        <v>104111612</v>
       </c>
       <c r="B16" t="n">
-        <v>89997</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5454</v>
+        <v>1975</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långa Komyr., Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>318307.8674563793</v>
+        <v>318356</v>
       </c>
       <c r="R16" t="n">
-        <v>6555000.705480744</v>
+        <v>6555087</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2562,22 +2494,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2590,83 +2512,67 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Blåbärbarrskog.</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Låga.</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tommy Solberg, Bård E. Andersen</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101986860</v>
+        <v>104111697</v>
       </c>
       <c r="B17" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>1975</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söder om Långa Komyr, Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>318287.3002075547</v>
+        <v>318357</v>
       </c>
       <c r="R17" t="n">
-        <v>6554969.266814172</v>
+        <v>6555088</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2693,22 +2599,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2729,65 +2625,59 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bård E. Andersen, Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101992255</v>
+        <v>104111779</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1975</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väst om Stickshöjden, Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>318448.3407579059</v>
+        <v>318427</v>
       </c>
       <c r="R18" t="n">
-        <v>6555147.36052313</v>
+        <v>6555099</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2814,22 +2704,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2841,11 +2721,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2862,41 +2737,40 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104073157</v>
+        <v>104111871</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1975</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2905,13 +2779,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>318742.2788992287</v>
+        <v>318469</v>
       </c>
       <c r="R19" t="n">
-        <v>6555454.454782909</v>
+        <v>6555123</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2935,22 +2809,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2963,76 +2827,55 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104073002</v>
+        <v>104111936</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1975</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -3041,13 +2884,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>318745.3427740743</v>
+        <v>318469</v>
       </c>
       <c r="R20" t="n">
-        <v>6555442.990806455</v>
+        <v>6555126</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3071,22 +2914,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3099,76 +2932,55 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104073032</v>
+        <v>104112069</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1975</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -3177,13 +2989,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>318744.4089167627</v>
+        <v>318548</v>
       </c>
       <c r="R21" t="n">
-        <v>6555455.897169326</v>
+        <v>6555249</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3207,22 +3019,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3237,7 +3039,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Bär- och ljungtallskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3252,55 +3054,50 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104073084</v>
+        <v>104203443</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1975</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3309,17 +3106,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Kroktjärnet O., Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>318746.5632868549</v>
+        <v>318138</v>
       </c>
       <c r="R22" t="n">
-        <v>6555457.852881978</v>
+        <v>6554823</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3343,22 +3140,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3373,22 +3160,12 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3406,37 +3183,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96478254</v>
+        <v>101934233</v>
       </c>
       <c r="B23" t="n">
-        <v>90139</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1975</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3449,14 +3221,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Söder om Långa Komyr, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>318431.7696957604</v>
+        <v>318287</v>
       </c>
       <c r="R23" t="n">
-        <v>6555102.354772438</v>
+        <v>6554970</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3483,22 +3255,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3539,67 +3301,55 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Bård E. Andersen, Tommy Solberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96473689</v>
+        <v>98968883</v>
       </c>
       <c r="B24" t="n">
-        <v>90139</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1975</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>318588.8616425463</v>
+        <v>318644</v>
       </c>
       <c r="R24" t="n">
-        <v>6555251.821991755</v>
+        <v>6555333</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3623,22 +3373,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3647,99 +3387,66 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96477946</v>
+        <v>112387478</v>
       </c>
       <c r="B25" t="n">
-        <v>90139</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1975</v>
+        <v>2569</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>318545.6723920377</v>
+        <v>318274</v>
       </c>
       <c r="R25" t="n">
-        <v>6555210.653741721</v>
+        <v>6554953</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3763,22 +3470,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3787,95 +3484,66 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson, Maria Johansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104073740</v>
+        <v>98968865</v>
       </c>
       <c r="B26" t="n">
-        <v>90139</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1975</v>
+        <v>2590</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>318525.5470916672</v>
+        <v>318448</v>
       </c>
       <c r="R26" t="n">
-        <v>6555188.456244989</v>
+        <v>6555118</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3899,22 +3567,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3923,96 +3581,71 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Bärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104112477</v>
+        <v>101986860</v>
       </c>
       <c r="B27" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>2590</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Söder om Långa Komyr, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>318418.591485857</v>
+        <v>318287</v>
       </c>
       <c r="R27" t="n">
-        <v>6555117.902467199</v>
+        <v>6554970</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4039,22 +3672,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4067,26 +3690,6 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -4095,64 +3698,60 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Bård E. Andersen, Tommy Solberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104112266</v>
+        <v>108741269</v>
       </c>
       <c r="B28" t="n">
-        <v>89997</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5454</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Väster om St.Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>318390.2307778532</v>
+        <v>318564</v>
       </c>
       <c r="R28" t="n">
-        <v>6555128.511945985</v>
+        <v>6555308</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4179,22 +3778,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4209,7 +3798,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Bär- och ljungtallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4224,7 +3813,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4242,61 +3831,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104112541</v>
+        <v>112387479</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>318430.7167266786</v>
+        <v>318300</v>
       </c>
       <c r="R29" t="n">
-        <v>6555101.890276681</v>
+        <v>6554978</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4320,22 +3896,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4344,84 +3910,81 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson, Maria Johansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104111779</v>
+        <v>112387480</v>
       </c>
       <c r="B30" t="n">
-        <v>90139</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1975</v>
+        <v>2590</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>318426.9703419526</v>
+        <v>318343</v>
       </c>
       <c r="R30" t="n">
-        <v>6555098.981107346</v>
+        <v>6555009</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4445,22 +4008,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4469,79 +4022,66 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson, Maria Johansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104111697</v>
+        <v>112387489</v>
       </c>
       <c r="B31" t="n">
-        <v>90139</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1975</v>
+        <v>2590</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>318356.8826498509</v>
+        <v>318179</v>
       </c>
       <c r="R31" t="n">
-        <v>6555088.419970584</v>
+        <v>6554817</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4565,22 +4105,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4589,79 +4119,66 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson, Maria Johansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104104854</v>
+        <v>120762661</v>
       </c>
       <c r="B32" t="n">
-        <v>90139</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1975</v>
+        <v>2671</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>318361.1922006097</v>
+        <v>318346</v>
       </c>
       <c r="R32" t="n">
-        <v>6555092.331386001</v>
+        <v>6555065</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4685,22 +4202,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4709,54 +4216,43 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Bär- och ljungtallskog</t>
-        </is>
-      </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson, Urban Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104112687</v>
+        <v>112387490</v>
       </c>
       <c r="B33" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4764,45 +4260,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>318470.1377448139</v>
+        <v>318132</v>
       </c>
       <c r="R33" t="n">
-        <v>6555139.636009235</v>
+        <v>6554787</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4826,22 +4314,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4850,99 +4328,66 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson, Maria Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104121129</v>
+        <v>119659936</v>
       </c>
       <c r="B34" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5685</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>318658.4541573614</v>
+        <v>318644</v>
       </c>
       <c r="R34" t="n">
-        <v>6555371.484271608</v>
+        <v>6555323</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4966,22 +4411,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4990,99 +4425,66 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104112069</v>
+        <v>120762662</v>
       </c>
       <c r="B35" t="n">
-        <v>90139</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1975</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>318548.0395805236</v>
+        <v>318394</v>
       </c>
       <c r="R35" t="n">
-        <v>6555249.644420044</v>
+        <v>6555065</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5106,22 +4508,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5130,99 +4522,66 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Bär- och ljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Låga utan markkontakt # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson, Urban Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>104111612</v>
+        <v>112387492</v>
       </c>
       <c r="B36" t="n">
-        <v>90139</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1975</v>
+        <v>4368</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>318355.8052607778</v>
+        <v>318045</v>
       </c>
       <c r="R36" t="n">
-        <v>6555087.442116776</v>
+        <v>6554742</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5246,22 +4605,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5270,79 +4619,66 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson, Maria Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>104112568</v>
+        <v>98968892</v>
       </c>
       <c r="B37" t="n">
-        <v>89851</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5467</v>
+        <v>4660</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>318453.4388419933</v>
+        <v>318663</v>
       </c>
       <c r="R37" t="n">
-        <v>6555124.479028849</v>
+        <v>6555312</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5366,22 +4702,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5390,93 +4716,81 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104074302</v>
+        <v>115283559</v>
       </c>
       <c r="B38" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>5260</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>St. Stickshöjden, Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>318640.909171818</v>
+        <v>318343</v>
       </c>
       <c r="R38" t="n">
-        <v>6555316.751329417</v>
+        <v>6555009</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5503,22 +4817,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5531,76 +4835,78 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson, Maria Johansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104203443</v>
+        <v>98968882</v>
       </c>
       <c r="B39" t="n">
-        <v>91087</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1975</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kroktjärnet O., Dls</t>
+          <t>Stora Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>318138</v>
+        <v>318637</v>
       </c>
       <c r="R39" t="n">
-        <v>6554823</v>
+        <v>6555325</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5624,12 +4930,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5638,44 +4944,43 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112387479</v>
+        <v>98968886</v>
       </c>
       <c r="B40" t="n">
-        <v>94448</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5683,21 +4988,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2590</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5707,10 +5012,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>318301</v>
+        <v>318704</v>
       </c>
       <c r="R40" t="n">
-        <v>6554977</v>
+        <v>6555406</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5737,12 +5042,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5756,17 +5061,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5777,57 +5082,55 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Larsson, Maria Johansson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112387478</v>
+        <v>101934586</v>
       </c>
       <c r="B41" t="n">
-        <v>95128</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2569</v>
+        <v>5454</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>Långa Komyr., Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>318275</v>
+        <v>318308</v>
       </c>
       <c r="R41" t="n">
-        <v>6554953</v>
+        <v>6555001</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5854,12 +5157,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5868,33 +5171,39 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Blåbärbarrskog.</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Låga.</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Larsson, Maria Johansson</t>
+          <t>Bård E. Andersen, Tommy Solberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112387492</v>
+        <v>104112266</v>
       </c>
       <c r="B42" t="n">
-        <v>90932</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5902,37 +5211,44 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4368</v>
+        <v>5454</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>318046</v>
+        <v>318391</v>
       </c>
       <c r="R42" t="n">
-        <v>6554741</v>
+        <v>6555128</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5956,12 +5272,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5970,33 +5286,49 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Bär- och ljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Larsson, Maria Johansson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119659936</v>
+        <v>101934034</v>
       </c>
       <c r="B43" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92398</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6004,34 +5336,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>5467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>Långa Komyr., Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>318644</v>
+        <v>318351</v>
       </c>
       <c r="R43" t="n">
-        <v>6555323</v>
+        <v>6555053</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6058,12 +5393,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6072,71 +5407,84 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Blåbärbarrskog.</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg, Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120762661</v>
+        <v>101934224</v>
       </c>
       <c r="B44" t="n">
-        <v>94562</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92398</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2671</v>
+        <v>5467</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>Söder om Långa Komyr, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>318346</v>
+        <v>318287</v>
       </c>
       <c r="R44" t="n">
-        <v>6555065</v>
+        <v>6554970</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6160,12 +5508,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2022-06-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6174,91 +5522,94 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anton Larsson, Urban Larsson</t>
+          <t>Bård E. Andersen, Tommy Solberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120762734</v>
+        <v>101991110</v>
       </c>
       <c r="B45" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92398</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>5467</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>Sydväst om Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>318043</v>
+        <v>318372</v>
       </c>
       <c r="R45" t="n">
-        <v>6554751</v>
+        <v>6555050</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6282,12 +5633,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6296,91 +5647,94 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Larsson, Urban Larsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120762733</v>
+        <v>104112568</v>
       </c>
       <c r="B46" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92398</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>5467</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stora Stickshöjden, Dls</t>
+          <t>St. Stickshöjden, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>318048</v>
+        <v>318454</v>
       </c>
       <c r="R46" t="n">
-        <v>6554747</v>
+        <v>6555124</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6404,12 +5758,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6418,9 +5772,15 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AJ46" t="inlineStr">
         <is>
           <t>tall</t>
@@ -6433,21 +5793,2399 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>96480542</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91282</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SV om Stora Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>318475</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6555213</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>96480625</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91282</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SV om Stora Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>318460</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6555146</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>101933733</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91282</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långa Komyr, Dls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>318246</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6554982</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Blåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tommy Solberg, Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>104121129</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91282</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>St. Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>318658</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6555372</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120762660</v>
+      </c>
+      <c r="B51" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stora Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>318296</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6555061</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
           <t>Anton Larsson</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>Anton Larsson, Urban Larsson</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>104073002</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>St. Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>318745</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6555443</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>104073032</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>St. Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>318744</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6555456</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>104073084</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>St. Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>318747</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6555458</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>104073157</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>St. Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>318742</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6555454</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>104073192</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>St. Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>318741</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6555469</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>98968896</v>
+      </c>
+      <c r="B57" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stora Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>318605</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6555315</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>98968889</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stora Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>318755</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6555388</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>98968884</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stora Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>318648</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6555348</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120762734</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stora Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>318043</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6554751</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Urban Larsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120762733</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stora Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>318048</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6554747</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Urban Larsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>101933803</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Långa Komyr S., Dls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>318265</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6554954</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Tommy Solberg, Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>101992255</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Väst om Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>318448</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6555147</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>104112541</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>St. Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>318431</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6555102</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>104074302</v>
+      </c>
+      <c r="B65" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>St. Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>318641</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6555317</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>98968879</v>
+      </c>
+      <c r="B66" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stora Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>318636</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6555290</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>112387491</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stora Stickshöjden, Dls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>318110</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6554767</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6469-2022 artfynd.xlsx
+++ b/artfynd/A 6469-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112687</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -923,6 +933,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96534476</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96481015</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1173,6 +1193,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112477</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1298,6 +1323,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96437745</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1423,6 +1453,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96473689</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1548,6 +1583,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96477946</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1673,6 +1713,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96478254</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1798,6 +1843,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96478596</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1923,6 +1973,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96479058</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2048,6 +2103,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96479440</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2173,6 +2233,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96479552</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2294,6 +2359,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073740</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2419,6 +2489,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104104854</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2524,6 +2599,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104111612</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2629,6 +2709,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104111697</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2734,6 +2819,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104111779</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2839,6 +2929,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104111871</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2944,6 +3039,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104111936</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3069,6 +3169,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112069</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3180,6 +3285,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104203443</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3305,6 +3415,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101934233</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3402,6 +3517,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98968883</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3499,6 +3619,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112387478</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3596,6 +3721,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98968865</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3702,6 +3832,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101986860</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3828,6 +3963,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108741269</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3940,6 +4080,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112387479</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4037,6 +4182,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112387480</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4134,6 +4284,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112387489</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4246,6 +4401,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120762661</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4343,6 +4503,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112387490</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4440,6 +4605,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119659936</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4537,6 +4707,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120762662</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4634,6 +4809,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112387492</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4746,6 +4926,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98968892</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4862,6 +5047,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115283559</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4974,6 +5164,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98968882</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5086,6 +5281,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98968886</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5197,6 +5397,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101934586</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5322,6 +5527,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112266</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5433,6 +5643,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101934034</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5558,6 +5773,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101934224</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5683,6 +5903,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101991110</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5808,6 +6033,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112568</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5933,6 +6163,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96480542</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6058,6 +6293,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96480625</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6179,6 +6419,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933733</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6304,6 +6549,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104121129</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6401,6 +6651,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120762660</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6522,6 +6777,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073002</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6643,6 +6903,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073032</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6764,6 +7029,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073084</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6885,6 +7155,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073157</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7006,6 +7281,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073192</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7103,6 +7383,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98968896</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7205,6 +7490,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98968889</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7307,6 +7597,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98968884</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7424,6 +7719,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120762734</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7541,6 +7841,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120762733</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7648,6 +7953,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101933803</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7759,6 +8069,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101992255</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7870,6 +8185,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104112541</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7977,6 +8297,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104074302</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8074,6 +8399,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98968879</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8186,8 +8516,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112387491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>